--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E38E7D-0297-B140-9BB2-F99469ED25C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4406F3-BDB5-2245-8879-9471F276DC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>n1XP8yo_gXY</t>
+  </si>
+  <si>
+    <t>hSzGRZKe3gY</t>
+  </si>
+  <si>
+    <t>04-Distributions</t>
   </si>
 </sst>
 </file>
@@ -868,6 +874,12 @@
       <c r="E8" t="s">
         <v>51</v>
       </c>
+      <c r="F8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4406F3-BDB5-2245-8879-9471F276DC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED90584F-F9C0-2B47-B3C5-B97AC0FC2CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="85">
   <si>
     <t>Date</t>
   </si>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>04-Distributions</t>
+  </si>
+  <si>
+    <t>05-Foundation_for_Inference</t>
+  </si>
+  <si>
+    <t>NlJwU7-u1lo</t>
   </si>
 </sst>
 </file>
@@ -899,6 +905,12 @@
       <c r="E9" t="s">
         <v>52</v>
       </c>
+      <c r="F9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" t="s">
+        <v>83</v>
+      </c>
       <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED90584F-F9C0-2B47-B3C5-B97AC0FC2CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BF60A3-F2BB-CA42-9310-B74DC92940AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -290,6 +290,12 @@
   </si>
   <si>
     <t>NlJwU7-u1lo</t>
+  </si>
+  <si>
+    <t>06-Infernce_for_Categorial_Data</t>
+  </si>
+  <si>
+    <t>AsTAHYMIXkc</t>
   </si>
 </sst>
 </file>
@@ -930,6 +936,12 @@
       <c r="E10" t="s">
         <v>53</v>
       </c>
+      <c r="F10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" t="s">
+        <v>85</v>
+      </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BF60A3-F2BB-CA42-9310-B74DC92940AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6C5430-9992-284D-8263-558806553813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -292,10 +292,10 @@
     <t>NlJwU7-u1lo</t>
   </si>
   <si>
-    <t>06-Infernce_for_Categorial_Data</t>
-  </si>
-  <si>
     <t>AsTAHYMIXkc</t>
+  </si>
+  <si>
+    <t>06-Inference_for_Categorical_Data</t>
   </si>
 </sst>
 </file>
@@ -937,10 +937,10 @@
         <v>53</v>
       </c>
       <c r="F10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" t="s">
         <v>86</v>
-      </c>
-      <c r="G10" t="s">
-        <v>85</v>
       </c>
       <c r="H10" s="4"/>
     </row>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6C5430-9992-284D-8263-558806553813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A36F82-8EB4-E143-8FA4-CB7D0FC0BE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t>06-Inference_for_Categorical_Data</t>
+  </si>
+  <si>
+    <t>FJObZwghANo</t>
+  </si>
+  <si>
+    <t>07-Inference_for_Numerical_Data</t>
   </si>
 </sst>
 </file>
@@ -961,6 +967,12 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
+      <c r="F11" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" t="s">
+        <v>88</v>
+      </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A36F82-8EB4-E143-8FA4-CB7D0FC0BE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AB3501-314A-EE4A-90B0-EC691BE11741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="91">
   <si>
     <t>Date</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>07-Inference_for_Numerical_Data</t>
+  </si>
+  <si>
+    <t>NnSFBSffs2w</t>
+  </si>
+  <si>
+    <t>08-Linear_Regression</t>
   </si>
 </sst>
 </file>
@@ -992,6 +998,12 @@
       <c r="E12" t="s">
         <v>55</v>
       </c>
+      <c r="F12" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" t="s">
+        <v>90</v>
+      </c>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AB3501-314A-EE4A-90B0-EC691BE11741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E498CE-944D-7D47-A5A9-0FA0291BD572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
   <si>
     <t>Date</t>
   </si>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t>08-Linear_Regression</t>
+  </si>
+  <si>
+    <t>08-Linear_Regression2</t>
+  </si>
+  <si>
+    <t>oB7mahqoLy8</t>
   </si>
 </sst>
 </file>
@@ -1023,6 +1029,12 @@
       <c r="E13" t="s">
         <v>55</v>
       </c>
+      <c r="F13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" t="s">
+        <v>91</v>
+      </c>
       <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E498CE-944D-7D47-A5A9-0FA0291BD572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C5324C-720E-C24A-8813-9870778CAB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -314,6 +314,12 @@
   </si>
   <si>
     <t>oB7mahqoLy8</t>
+  </si>
+  <si>
+    <t>09-Logistic_Regression</t>
+  </si>
+  <si>
+    <t>EL9PFomZqBg</t>
   </si>
 </sst>
 </file>
@@ -1054,6 +1060,12 @@
       <c r="E14" t="s">
         <v>56</v>
       </c>
+      <c r="F14" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" t="s">
+        <v>93</v>
+      </c>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C5324C-720E-C24A-8813-9870778CAB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2106C71C-E1F7-1E45-B3CA-64DA7237F2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>EL9PFomZqBg</t>
+  </si>
+  <si>
+    <t>7-S6Ccv2-5M</t>
+  </si>
+  <si>
+    <t>09-Multiple_Regression</t>
   </si>
 </sst>
 </file>
@@ -1094,6 +1100,12 @@
       <c r="E16" t="s">
         <v>56</v>
       </c>
+      <c r="F16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2106C71C-E1F7-1E45-B3CA-64DA7237F2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38195F11-980F-174B-9A04-0CF270ECE681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="99">
   <si>
     <t>Date</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>09-Multiple_Regression</t>
+  </si>
+  <si>
+    <t>10-Bayesian_Analysis</t>
+  </si>
+  <si>
+    <t>1P7ayb5rLmw</t>
   </si>
 </sst>
 </file>
@@ -1124,6 +1130,12 @@
       <c r="E17" t="s">
         <v>57</v>
       </c>
+      <c r="F17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Spring/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38195F11-980F-174B-9A04-0CF270ECE681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9937BF-B9E6-3346-B240-C1AC58E80EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="10920" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t>1P7ayb5rLmw</t>
+  </si>
+  <si>
+    <t>YRtvSP5m5-w</t>
+  </si>
+  <si>
+    <t>11-Final_Meetup</t>
   </si>
 </sst>
 </file>
@@ -1152,6 +1158,12 @@
       <c r="D18" t="s">
         <v>35</v>
       </c>
+      <c r="F18" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" t="s">
+        <v>100</v>
+      </c>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
